--- a/results/result_evaluation_logs/C_Error_Incorporation_Gen1.xlsx
+++ b/results/result_evaluation_logs/C_Error_Incorporation_Gen1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,11 +542,6 @@
       <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Result String</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Langfuse Trace ID</t>
         </is>
       </c>
     </row>
@@ -629,11 +624,6 @@
 </t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>8b49b772-8d1d-4bfe-a7c0-f09f7fb90579</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -709,11 +699,6 @@
 &lt;http://www.wikidata.org/entity/Q20992419&gt; wd:P31 &lt;http://www.wikidata.org/entity/Q17516&gt; .
 &lt;http://www.wikidata.org/entity/Q20992419&gt; wd:P585 &lt;http://www.wikidata.org/entity/Q120&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>db8fe5bf-e2aa-4fd8-b1a9-b1a116ec5e99</t>
         </is>
       </c>
     </row>
@@ -794,11 +779,6 @@
 </t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>e35c6580-6d46-404c-98b7-1e1636204408</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -814,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -823,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -832,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -853,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -862,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -885,11 +865,6 @@
 </t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>179676ab-a5ce-4b30-b776-1b217d6c8722</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -967,11 +942,6 @@
 </t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>386258ef-d2b5-47a2-9f03-8478beab155e</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1047,11 +1017,6 @@
 &lt;http://www.wikidata.org/entity/Q506252&gt; wd:P366 &lt;http://www.wikidata.org/entity/Q177&gt; .
 &lt;http://www.wikidata.org/entity/Q506252&gt; wd:P31 &lt;http://www.wikidata.org/entity/Q192786&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>b89277ef-bd19-454b-9a27-14f3b2660ab2</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1099,6 @@
 </t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>209cc353-4317-4d5c-94c5-99da4fedd915</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1218,11 +1178,6 @@
 </t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>d50a08a9-03f1-46af-8e84-32e10df10bb8</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1238,7 +1193,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1247,7 +1202,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1256,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1277,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1286,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1352,11 +1307,6 @@
 </t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7eb8e81b-651a-4493-93d1-ab86af0a9f0b</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1437,11 +1387,6 @@
 </t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>545efe32-5c18-402b-ab38-cd822f5c3097</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1520,11 +1465,6 @@
 </t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>607033af-4ff1-4d8a-840c-e03afc8256f5</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1602,11 +1542,6 @@
 </t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>574954d2-30ef-4e0a-a75f-4587230fbee1</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1684,11 +1619,6 @@
 </t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>fed9c279-784f-471a-897e-8e97c8b6976b</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1728,16 +1658,16 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>4</v>
@@ -1771,11 +1701,6 @@
 </t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>70fe7fda-91e3-4c0f-af6d-c2e56d081feb</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1854,11 +1779,6 @@
 </t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>c1506f93-c9cb-4dd6-bad5-1fc0b1f95bec</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1936,11 +1856,6 @@
 </t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>a291fb09-ebbb-4595-a08d-8a68d9d8fd1a</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2016,11 +1931,6 @@
 &lt;http://www.wikidata.org/entity/Q607380&gt; wd:P1056 &lt;http://www.wikidata.org/entity/Q6933370&gt; .
 &lt;http://www.wikidata.org/entity/Q6933370&gt; wd:P1056 &lt;http://www.wikidata.org/entity/Q607380&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>4b0ccaf7-e8d3-458b-a7ed-8adc4cd04c34</t>
         </is>
       </c>
     </row>
@@ -2105,11 +2015,6 @@
 </t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>f427f159-d4f5-4317-b00a-7788c82af7d2</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2186,11 +2091,6 @@
 &lt;http://www.wikidata.org/entity/Q20671544&gt; wd:P569 &lt;http://www.wikidata.org/entity/Q27914&gt; .
 &lt;http://www.wikidata.org/entity/Q20671544&gt; &lt;http://www.wikidata.org/entity/P569&gt; &lt;http://www.wikidata.org/entity/Q27914&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2f540f6e-3508-43ab-9ecc-012fb733e3e0</t>
         </is>
       </c>
     </row>
@@ -2273,11 +2173,6 @@
 </t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>b333187d-fe75-4d2d-abdc-07a7f6232f85</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2355,11 +2250,6 @@
 </t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>9bf2d48d-360a-4b2d-ae8f-3facc3578b2b</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2375,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2384,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2393,7 +2283,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2414,7 +2304,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -2423,7 +2313,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2489,11 +2379,6 @@
 </t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>5040a6b7-970b-455e-a1c3-38cfae1488fd</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2509,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2518,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2527,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2548,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2557,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2623,11 +2508,6 @@
 </t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>8b03e726-3858-43ad-82d2-ec8b93ca9e74</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2706,11 +2586,6 @@
 </t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>4baf67cc-26a8-495e-817f-f11d6c6efe69</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2726,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2735,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2744,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2765,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -2774,7 +2649,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2840,11 +2715,6 @@
 </t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>c5d016dc-7620-4866-8ad9-fb18ca126e73</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2922,11 +2792,6 @@
 </t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>a8db0e4d-e4de-4b5b-90cc-1e34cf050740</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2972,10 +2837,10 @@
         <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
         <v>2</v>
@@ -3003,11 +2868,6 @@
 &lt;http://www.wikidata.org/entity/Q22082365&gt; &lt;http://www.wikidata.org/entity/P361&gt; &lt;http://www.wikidata.org/entity/Q965&gt; .
 &lt;http://www.wikidata.org/entity/Q965&gt; &lt;http://www.wikidata.org/entity/P463&gt; &lt;http://www.wikidata.org/entity/Q47543&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>3bb8a05d-d86d-46f7-ae94-bc78803aca31</t>
         </is>
       </c>
     </row>
@@ -3091,11 +2951,6 @@
 </t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>d64b8a9c-c5db-45af-88b5-b3ffc7aa1dde</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3111,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -3120,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3129,7 +2984,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -3150,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -3159,7 +3014,7 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -3225,11 +3080,6 @@
 </t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>1133efb8-92ef-4742-838d-76167e099108</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3245,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -3254,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -3263,7 +3113,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -3284,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3293,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -3359,11 +3209,6 @@
 </t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>6b6ae572-0275-44d0-90a6-d534e59e395e</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3409,10 +3254,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
@@ -3441,11 +3286,6 @@
 &lt;http://www.wikidata.org/entity/Q65090308&gt; wd:P674 &lt;http://www.wikidata.org/entity/Q64876878&gt; .
 &lt;http://www.wikidata.org/entity/Q262170&gt; wd:P725 &lt;http://www.wikidata.org/entity/Q64876878&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>0472f7b0-ada4-45ce-bf40-189fdd725063</t>
         </is>
       </c>
     </row>
@@ -3530,11 +3370,6 @@
 </t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>7e8c5850-e707-43e5-bd59-960fe45b8a48</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3614,11 +3449,6 @@
 </t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>56b409b7-acd2-4aa9-b0cf-baf5442df4a4</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3694,11 +3524,6 @@
 &lt;http://www.wikidata.org/entity/Q41792848&gt; wd:P2515 &lt;http://www.wikidata.org/entity/Q5072388&gt; .
 &lt;http://www.wikidata.org/entity/Q5072388&gt; wd:P162 &lt;http://www.wikidata.org/entity/Q41792848&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>b1ebae5c-fb79-4380-8bb0-189dbea104a0</t>
         </is>
       </c>
     </row>
@@ -3779,11 +3604,6 @@
 </t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>72747277-081d-428a-bbc1-934a9e0b3955</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3862,11 +3682,6 @@
 </t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2579e6c0-c452-4399-81e2-454091766550</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3882,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -3891,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3900,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -3921,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -3930,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -3996,11 +3811,6 @@
 </t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>66e5e7ab-7582-4681-9834-8ba964781cec</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4078,11 +3888,6 @@
 </t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>9c21e0e7-1195-4b27-87e4-ce2cfcc1f3ca</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4158,11 +3963,6 @@
 &lt;http://www.wikidata.org/entity/Q1064344&gt; wd:P177 &lt;http://www.wikidata.org/entity/Q1406&gt; .
 &lt;http://www.wikidata.org/entity/Q1064344&gt; wd:P162 &lt;http://www.wikidata.org/entity/Q1406&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>e1cf7026-bb3a-41a4-be3c-a67e86f01cf4</t>
         </is>
       </c>
     </row>
@@ -4243,11 +4043,6 @@
 </t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>67c43381-c9ea-4f5a-8dcd-26ad195a391e</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4293,10 +4088,10 @@
         <v>4</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
@@ -4332,11 +4127,6 @@
 </t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>3d81cb2b-5ef6-4d33-98ea-f8a292e7717d</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4416,11 +4206,6 @@
 </t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>2faf557d-2278-4dff-bbf1-6dd3b95bd8d8</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4497,11 +4282,6 @@
 &lt;http://www.wikidata.org/entity/Q29644512&gt; wd:P31 &lt;http://www.wikidata.org/entity/Q1358919&gt; .
 &lt;http://www.wikidata.org/entity/Q29644512&gt; wd:P826 &lt;http://www.wikidata.org/entity/Q152074&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>de717628-fd57-452a-9cdd-486776e12c76</t>
         </is>
       </c>
     </row>
@@ -4586,11 +4366,6 @@
 </t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>b9569144-7319-40df-853c-bd336830422f</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4669,11 +4444,6 @@
 </t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>8dd422cb-e0af-467f-a374-385c382f42c4</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4750,11 +4520,6 @@
 </t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>bfeff215-e5ef-4cec-86b0-d67fedeb4e8b</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4800,10 +4565,10 @@
         <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="n">
         <v>4</v>
@@ -4842,11 +4607,6 @@
 </t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>79edca74-2b2d-4bee-bbbd-8b16abdf7a20</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4886,16 +4646,16 @@
         <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
@@ -4924,11 +4684,6 @@
 &lt;http://www.wikidata.org/entity/Q199131&gt; wd:P1366 &lt;http://www.wikidata.org/entity/Q173071&gt; .
 &lt;http://www.wikidata.org/entity/Q199131&gt; wd:P156 &lt;http://www.wikidata.org/entity/Q173071&gt; .
 </t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>37b45f49-b29d-414f-aa03-0cad019fb8c6</t>
         </is>
       </c>
     </row>
@@ -5012,11 +4767,6 @@
 </t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>666381dd-e7be-458a-9132-53fb4b248d2b</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5095,11 +4845,6 @@
 </t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>47181480-2acf-4ab0-b75c-b40d419dc74a</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
